--- a/forms/trg/Formulir_TRG_futropicrops.xlsx
+++ b/forms/trg/Formulir_TRG_futropicrops.xlsx
@@ -951,7 +951,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
@@ -984,7 +984,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D19" s="12" t="n"/>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D20" s="12" t="n"/>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D21" s="12" t="n"/>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D22" s="12" t="n"/>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D23" s="12" t="n"/>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D24" s="12" t="n"/>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D26" s="12" t="n"/>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D27" s="12" t="n"/>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D28" s="12" t="n"/>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D29" s="12" t="n"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D30" s="12" t="n"/>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D31" s="12" t="n"/>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D32" s="12" t="n"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D33" s="12" t="n"/>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D34" s="12" t="n"/>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D35" s="12" t="n"/>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D36" s="12" t="n"/>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D37" s="12" t="n"/>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D38" s="12" t="n"/>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D39" s="12" t="n"/>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D40" s="12" t="n"/>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D41" s="12" t="n"/>
